--- a/docs/bulk-templates/tasks_boarding_sample.xlsx
+++ b/docs/bulk-templates/tasks_boarding_sample.xlsx
@@ -695,7 +695,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Store the installation is for (must exist), e.g. ST-001.</t>
+          <t>Mandatory. Store the installation is for (must exist), e.g. ST-001.</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Must be an artwork of that brand.</t>
+          <t>Artwork name / code. Must be an artwork of that brand.</t>
         </is>
       </c>
     </row>

--- a/docs/bulk-templates/tasks_boarding_sample.xlsx
+++ b/docs/bulk-templates/tasks_boarding_sample.xlsx
@@ -450,7 +450,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -465,7 +465,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>store_uid</t>
+          <t>customer_code</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -497,7 +497,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ST-101</t>
+          <t>YG000000026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ST-102</t>
+          <t>YG000000033</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ST-104</t>
+          <t>YG000000038</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
@@ -565,7 +565,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ST-103</t>
+          <t>YG000000037</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ST-105</t>
+          <t>YG000101108</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
@@ -609,7 +609,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ST-106</t>
+          <t>YG000101109</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -643,7 +643,7 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
@@ -685,7 +685,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>store_uid</t>
+          <t>customer_code</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mandatory. Store the installation is for (must exist), e.g. ST-001.</t>
+          <t>Mandatory. Customer Code of the store the installation is for (must exist).</t>
         </is>
       </c>
     </row>

--- a/docs/bulk-templates/tasks_boarding_sample.xlsx
+++ b/docs/bulk-templates/tasks_boarding_sample.xlsx
@@ -460,32 +460,32 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>vendor_uid</t>
+          <t>VENDOR_UID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>customer_code</t>
+          <t>CUSTOMER_CODE</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>brand_name</t>
+          <t>BRAND_NAME</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>artwork_name</t>
+          <t>ARTWORK_NAME</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>width_in</t>
+          <t>WIDTH_IN</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>height_in</t>
+          <t>HEIGHT_IN</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>vendor_uid</t>
+          <t>VENDOR_UID</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -685,7 +685,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>customer_code</t>
+          <t>CUSTOMER_CODE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>brand_name</t>
+          <t>BRAND_NAME</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>artwork_name</t>
+          <t>ARTWORK_NAME</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -736,7 +736,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>width_in</t>
+          <t>WIDTH_IN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>height_in</t>
+          <t>HEIGHT_IN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">

--- a/docs/bulk-templates/tasks_boarding_sample.xlsx
+++ b/docs/bulk-templates/tasks_boarding_sample.xlsx
@@ -452,7 +452,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
@@ -500,16 +500,8 @@
           <t>YG000000026</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>BrandX</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>BrandX-Festive-2026</t>
-        </is>
-      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="n">
         <v>48</v>
       </c>
@@ -528,11 +520,7 @@
           <t>YG000000033</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>BrandX</t>
-        </is>
-      </c>
+      <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="n">
         <v>60</v>
@@ -568,11 +556,7 @@
           <t>YG000000037</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>BrandX</t>
-        </is>
-      </c>
+      <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="n">
         <v>36</v>
@@ -612,16 +596,8 @@
           <t>YG000101109</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>BrandX</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>BrandX-Festive-2026</t>
-        </is>
-      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="n">
         <v>48</v>
       </c>
@@ -712,7 +688,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Must match an existing brand.</t>
+          <t>Must match a brand that already exists in the system (Manage &gt; Brands). Left blank in the sample because brand names differ per system.</t>
         </is>
       </c>
     </row>

--- a/docs/bulk-templates/tasks_boarding_sample.xlsx
+++ b/docs/bulk-templates/tasks_boarding_sample.xlsx
@@ -73,12 +73,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -616,134 +619,144 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="60" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Notes</t>
+          <t>Column names are matched on SPELLING ONLY. Upper or lower case makes no difference, and spaces, hyphens and underscores are treated the same - so CUST_CD, Cust_CD and "cust cd" are the same column. The headers on the Data sheet are all-caps; keep the wording, and the case is up to you. A sheet filled in with Caps Lock on uploads exactly like any other. Do not rename, reorder or delete columns - only the wording identifies them.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
           <t>VENDOR_UID</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Vendor the task is for (must exist), e.g. VND-001.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>CUSTOMER_CODE</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Mandatory. Customer Code of the store the installation is for (must exist).</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>BRAND_NAME</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Must match a brand that already exists in the system (Manage &gt; Brands). Left blank in the sample because brand names differ per system.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>ARTWORK_NAME</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Artwork name / code. Must be an artwork of that brand.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>WIDTH_IN</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Board width in inches (e.g. 48). Pair with height_in.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>HEIGHT_IN</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Board height in inches (e.g. 36). Pair with width_in.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>